--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamruddhiShirole\Documents\UiPath\ConocoPhillips_performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7148E8-FE37-4F70-9F1E-54A14A030BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343B5CC2-2B2A-4537-AC94-BEC19EEED5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="0" windowWidth="14620" windowHeight="10080" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="268">
   <si>
     <t>Name</t>
   </si>
@@ -695,9 +695,6 @@
     <t>Meter Number,Meter Name,Production Date,Pressure Base,MCF,MMBTU</t>
   </si>
   <si>
-    <t>ConocoPhillips_Queue</t>
-  </si>
-  <si>
     <t>du_ConocoPhillip_Project_resources</t>
   </si>
   <si>
@@ -710,31 +707,10 @@
     <t>APIKEY</t>
   </si>
   <si>
-    <t>Meter Number Confidence</t>
-  </si>
-  <si>
-    <t>Meter Name Confidence</t>
-  </si>
-  <si>
-    <t>Production Date Confidence</t>
-  </si>
-  <si>
-    <t>Pressure Base Confidence</t>
-  </si>
-  <si>
-    <t>MCF Confidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MMBTU Confidence</t>
-  </si>
-  <si>
     <t>Conocoproject</t>
   </si>
   <si>
     <t>OutputFolderPath</t>
-  </si>
-  <si>
-    <t>Data\Output</t>
   </si>
   <si>
     <t>Folder path where output Excel file will be saved</t>
@@ -922,6 +898,134 @@
   </si>
   <si>
     <t>Meter Number,Meter Name,Production Date,BTU,Pressure Base,Basis,Allocation Decimal,MCF,MMBTU,Gas Lift MCF,Gas Lift MMBTU,Diverted Gas MCF,Diverted Gas MMBTU</t>
+  </si>
+  <si>
+    <t>C:\Users\SamruddhiShirole\Documents\UiPath\ConocoPhillips_performer\Data\Output</t>
+  </si>
+  <si>
+    <t>StartmailBody</t>
+  </si>
+  <si>
+    <t>&lt;html&gt;
+&lt;head&gt;
+&lt;style&gt;
+body{
+    margin:0;
+    padding:0;
+    background-color:#f4f6f8;
+    font-family:Arial, Helvetica, sans-serif;
+}
+.container{
+    max-width:600px;
+    margin:30px auto;
+    background:#ffffff;
+    border-radius:10px;
+    overflow:hidden;
+    box-shadow:0 4px 12px rgba(0,0,0,0.08);
+}
+.header{
+    background:#1f4e78;
+    color:#ffffff;
+    text-align:center;
+    padding:20px;
+    font-size:24px;
+    font-weight:bold;
+}
+.content{
+    padding:30px;
+    color:#333333;
+    font-size:15px;
+    line-height:1.6;
+}
+.info-box{
+    background:#f8fafc;
+    border-left:4px solid #1f4e78;
+    padding:15px;
+    margin-top:20px;
+    border-radius:5px;
+}
+.label{
+    font-weight:bold;
+    color:#1f4e78;
+}
+.footer{
+    text-align:center;
+    font-size:12px;
+    color:#888888;
+    padding:15px;
+    background:#f9f9f9;
+}
+&lt;/style&gt;
+&lt;/head&gt;
+&lt;body&gt;
+&lt;div class="container"&gt;
+    &lt;div class="header"&gt;
+        Process Started
+    &lt;/div&gt;
+    &lt;div class="content"&gt;
+        &lt;p&gt;Hello Team,&lt;/p&gt;
+        &lt;p&gt;The automation process has started successfully.&lt;/p&gt;
+        &lt;div class="info-box"&gt;
+            &lt;p&gt;&lt;span class="label"&gt;Process Name:&lt;/span&gt; {ProcessName}&lt;/p&gt;
+            &lt;p&gt;&lt;span class="label"&gt;Start Time:&lt;/span&gt; {StartTime}&lt;/p&gt;
+            &lt;p&gt;&lt;span class="label"&gt;Status:&lt;/span&gt; In Progress&lt;/p&gt;
+        &lt;/div&gt;
+        &lt;p&gt;Please find the completion summary in the final notification email once processing is completed.&lt;/p&gt;
+    &lt;/div&gt;
+    &lt;div class="footer"&gt;
+        This is an automated system generated email.
+    &lt;/div&gt;
+&lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;</t>
+  </si>
+  <si>
+    <t>startmailsubject</t>
+  </si>
+  <si>
+    <t>Conoproject started</t>
+  </si>
+  <si>
+    <t>Starting Statement Post Processing</t>
+  </si>
+  <si>
+    <t>LogMessage_StatementPostProcessing</t>
+  </si>
+  <si>
+    <t>These are the fields that failed:</t>
+  </si>
+  <si>
+    <t>LogMessage_StatementPostProcessing_MandatoryFieldsFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_StatementPostProcessing_AlreadySetFalse</t>
+  </si>
+  <si>
+    <t>LogMessage_StatementPostProcessing_ConfidenceFieldsFailure</t>
+  </si>
+  <si>
+    <t>ConocoPhillipsQueue</t>
+  </si>
+  <si>
+    <t>Shared</t>
+  </si>
+  <si>
+    <t>Meter Number-Confidence</t>
+  </si>
+  <si>
+    <t>Meter Name-Confidence</t>
+  </si>
+  <si>
+    <t>Production Date-Confidence</t>
+  </si>
+  <si>
+    <t>Pressure Base-Confidence</t>
+  </si>
+  <si>
+    <t>MCF-Confidence</t>
+  </si>
+  <si>
+    <t>MMBTU-Confidence</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1630,7 @@
         <v>135</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>151</v>
@@ -1589,7 +1693,7 @@
         <v>192</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
         <v>193</v>
@@ -1617,7 +1721,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C27" t="s">
         <v>159</v>
@@ -1628,7 +1732,7 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C28" t="s">
         <v>160</v>
@@ -1639,7 +1743,7 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C29" t="s">
         <v>161</v>
@@ -1650,7 +1754,7 @@
         <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C30" t="s">
         <v>162</v>
@@ -1661,7 +1765,7 @@
         <v>77</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="C31" t="s">
         <v>163</v>
@@ -1672,7 +1776,7 @@
         <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
         <v>164</v>
@@ -1680,70 +1784,70 @@
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B34" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1"/>
@@ -1756,43 +1860,55 @@
     <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
-      <c r="B53" s="2"/>
+      <c r="A53" t="s">
+        <v>250</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="55" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A55" t="s">
+        <v>252</v>
+      </c>
+      <c r="B55" t="s">
+        <v>253</v>
+      </c>
+    </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
@@ -4292,10 +4408,10 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -5339,7 +5455,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5007CE1-A05D-4745-B7EA-4E0BD0A3B111}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="57.54296875" bestFit="1" customWidth="1"/>
@@ -5382,7 +5498,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -5390,7 +5506,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="B5">
         <v>80</v>
@@ -5398,7 +5514,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="B6">
         <v>80</v>
@@ -5406,7 +5522,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B7">
         <v>75</v>
@@ -5414,7 +5530,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="B8">
         <v>75</v>
@@ -5422,10 +5538,42 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="B9">
         <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
